--- a/OMI_Questions_Review.xlsx
+++ b/OMI_Questions_Review.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,6 +497,11 @@
           <t>Option 5 (score 5)</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Option 6 (Not sure / N-A)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -548,6 +554,11 @@
           <t>Full business transaction observability — IT metrics linked to business SLAs, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -600,6 +611,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to business KPIs.</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -652,6 +668,11 @@
           <t>A unified Business Observability platform — IT and business share a single source of truth.</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -704,6 +725,11 @@
           <t>Fully automated synthetic testing in production and pre-prod with business-impact scoring per journey.</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -756,6 +782,11 @@
           <t>Full alignment — observability drives business SLA reporting, regulatory submissions, and P&amp;L impact assessments.</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -808,6 +839,11 @@
           <t>Full business transaction observability — IT metrics linked to business SLAs, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -860,6 +896,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to business KPIs.</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -912,6 +953,11 @@
           <t>A unified Business Observability platform — IT and business share a single source of truth.</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -964,6 +1010,11 @@
           <t>Fully automated synthetic testing across all channels with business-impact scoring per journey.</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1016,6 +1067,11 @@
           <t>Full alignment — observability drives regulatory submissions, SLA reporting, and business impact assessments.</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1068,6 +1124,11 @@
           <t>Full business transaction observability — IT metrics linked to business SLAs, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1120,6 +1181,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to business KPIs.</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1172,6 +1238,11 @@
           <t>A unified Business Observability platform — IT and business share a single source of truth.</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1224,6 +1295,11 @@
           <t>Fully automated synthetic testing across all channels with business-impact scoring per journey.</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1276,6 +1352,11 @@
           <t>Full alignment — observability directly feeds regulatory reporting, incident notifications, and board-level resilience scorecards.</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1328,6 +1409,11 @@
           <t>Full payment orchestration observability — each instrument mapped to SLA targets, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1380,6 +1466,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to settlement SLAs.</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1432,6 +1523,11 @@
           <t>A unified payments observability platform — IT, finance, and compliance share one view.</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1484,6 +1580,11 @@
           <t>All third-party dependencies are part of end-to-end transaction observability with business-impact scoring.</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1536,6 +1637,11 @@
           <t>Full alignment — observability directly feeds regulatory reporting, merchant SLAs, and chargeback analysis.</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1588,6 +1694,11 @@
           <t>Full payment orchestration observability — every instrument mapped to SLA targets, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1640,6 +1751,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to settlement SLAs.</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1692,6 +1808,11 @@
           <t>A unified payments observability platform — IT, finance, and compliance share one live view.</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1744,6 +1865,11 @@
           <t>All third-party dependencies are part of end-to-end transaction observability with business-impact scoring.</t>
         </is>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1796,6 +1922,11 @@
           <t>Full alignment — observability directly feeds scheme reporting, merchant SLA dashboards, and chargeback analysis.</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1848,6 +1979,11 @@
           <t>Full citizen service observability — IT metrics linked to programme SLAs and citizen experience outcomes.</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1900,6 +2036,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection with automated escalation to the programme team.</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1952,6 +2093,11 @@
           <t>A unified digital service observability platform — IT and programme management share one view.</t>
         </is>
       </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2004,6 +2150,11 @@
           <t>Fully automated synthetic testing with business-impact scoring per citizen service.</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2056,6 +2207,11 @@
           <t>Full alignment — observability feeds programme KPI dashboards, ministerial reporting, and audit submissions.</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2108,6 +2264,11 @@
           <t>Full citizen service observability — IT metrics linked to programme SLAs and citizen experience outcomes.</t>
         </is>
       </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2160,6 +2321,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection with automated escalation to the programme team.</t>
         </is>
       </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2212,6 +2378,11 @@
           <t>A unified digital service observability platform — IT and programme management share one live view.</t>
         </is>
       </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2264,6 +2435,11 @@
           <t>Fully automated synthetic testing with business-impact scoring per citizen service.</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2316,6 +2492,11 @@
           <t>Full alignment — observability feeds programme dashboards, ministerial reporting, and audit submissions.</t>
         </is>
       </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2368,6 +2549,11 @@
           <t>Full product observability — every customer journey mapped to SLA targets with automated triage on failure.</t>
         </is>
       </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2420,6 +2606,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection with deployment context and customer impact scoring.</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2472,6 +2663,11 @@
           <t>A unified product observability platform shared by engineering, CS, and account management.</t>
         </is>
       </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2524,6 +2720,11 @@
           <t>Continuous synthetic testing in production and staging with business-impact scoring per journey.</t>
         </is>
       </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2576,6 +2777,11 @@
           <t>Full alignment — observability feeds customer SLA reporting, renewal risk dashboards, and executive scorecards.</t>
         </is>
       </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2628,6 +2834,11 @@
           <t>Full omnichannel transaction observability — every customer journey mapped to conversion and revenue KPIs with automated triage.</t>
         </is>
       </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2680,6 +2891,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to GMV and conversion metrics.</t>
         </is>
       </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2732,6 +2948,11 @@
           <t>A unified commerce observability platform — IT, merchandising, and commercial share one live view.</t>
         </is>
       </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2784,6 +3005,11 @@
           <t>Continuous synthetic testing with GMV-impact scoring per journey degradation.</t>
         </is>
       </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2836,6 +3062,11 @@
           <t>Full alignment — observability directly drives incident prioritisation, sale-event capacity planning, and P&amp;L impact reporting.</t>
         </is>
       </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2888,6 +3119,11 @@
           <t>Full omnichannel transaction observability — every customer journey mapped to conversion and revenue KPIs with automated triage.</t>
         </is>
       </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2940,6 +3176,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to GMV and conversion metrics.</t>
         </is>
       </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2992,6 +3233,11 @@
           <t>A unified commerce observability platform — IT, merchandising, and commercial share one live view.</t>
         </is>
       </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3044,6 +3290,11 @@
           <t>Continuous synthetic testing with GMV-impact scoring per journey degradation.</t>
         </is>
       </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3096,6 +3347,11 @@
           <t>Full alignment — observability directly drives incident prioritisation, peak-event capacity planning, and revenue impact reporting.</t>
         </is>
       </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3148,6 +3404,11 @@
           <t>Full end-to-end service observability — network, IT, and BSS metrics linked to subscriber experience KPIs with automated triage.</t>
         </is>
       </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3200,6 +3461,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to subscriber experience and ARPU impact.</t>
         </is>
       </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3252,6 +3518,11 @@
           <t>A unified telecom service observability platform shared across NOC, commercial, CX, and regulatory functions.</t>
         </is>
       </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3304,6 +3575,11 @@
           <t>Continuous synthetic service testing with subscriber experience scoring and automated incident creation.</t>
         </is>
       </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3356,6 +3632,11 @@
           <t>Full alignment — observability feeds TRAI regulatory submissions, interconnect SLA reporting, and subscriber experience dashboards.</t>
         </is>
       </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3408,6 +3689,11 @@
           <t>Full end-to-end service observability — network, IT, and BSS metrics linked to subscriber experience KPIs with automated triage.</t>
         </is>
       </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3460,6 +3746,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to subscriber experience and ARPU impact.</t>
         </is>
       </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3512,6 +3803,11 @@
           <t>A unified telecom service observability platform shared across NOC, commercial, CX, and regulatory functions.</t>
         </is>
       </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3564,6 +3860,11 @@
           <t>Continuous synthetic service testing with subscriber experience scoring and automated incident creation.</t>
         </is>
       </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3616,6 +3917,11 @@
           <t>Full alignment — observability feeds regulatory submissions, interconnect SLA reporting, and subscriber experience dashboards.</t>
         </is>
       </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3668,6 +3974,11 @@
           <t>Full operational transaction observability — SCADA, OMS, billing, and metering linked to regulatory SLAs with automated triage.</t>
         </is>
       </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3720,6 +4031,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to grid SLAs and regulatory reliability indices.</t>
         </is>
       </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3772,6 +4088,11 @@
           <t>A unified utility operations platform — grid, commercial, and regulatory teams share one live view.</t>
         </is>
       </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3824,6 +4145,11 @@
           <t>Continuous end-to-end operational monitoring with regulatory reliability impact scoring.</t>
         </is>
       </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3876,6 +4202,11 @@
           <t>Full alignment — observability directly feeds regulatory submissions, SAIDI/SAIFI reporting, and tariff proceedings.</t>
         </is>
       </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3928,6 +4259,11 @@
           <t>Full operational transaction observability — SCADA, OMS, billing, and metering linked to regulatory SLAs with automated triage.</t>
         </is>
       </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3980,6 +4316,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to grid SLAs and regulatory reliability indices.</t>
         </is>
       </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4032,6 +4373,11 @@
           <t>A unified utility operations platform — grid, commercial, and regulatory teams share one live view.</t>
         </is>
       </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4084,6 +4430,11 @@
           <t>Continuous end-to-end operational monitoring with regulatory reliability impact scoring.</t>
         </is>
       </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4136,6 +4487,11 @@
           <t>Full alignment — observability directly feeds regulatory submissions, reliability index reporting, and tariff proceedings.</t>
         </is>
       </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4188,6 +4544,11 @@
           <t>Full manufacturing transaction observability — ERP, MES, SCADA, and QMS metrics linked to delivery and quality SLAs with automated triage.</t>
         </is>
       </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4240,6 +4601,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to OEE and delivery SLA impact.</t>
         </is>
       </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4292,6 +4658,11 @@
           <t>A unified manufacturing intelligence platform — operations, supply chain, quality, and commercial share one live view.</t>
         </is>
       </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4344,6 +4715,11 @@
           <t>Continuous end-to-end operational health monitoring with OEE and delivery commitment impact scoring.</t>
         </is>
       </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4394,6 +4770,11 @@
       <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Full alignment — observability directly drives incident prioritisation, capacity planning, and customer delivery SLA reporting.</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4421,6 +4802,7 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4474,6 +4856,11 @@
           <t>Option 5 (score 5)</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Option 6 (Not sure / N-A)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4526,6 +4913,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulatory reporting.</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4578,6 +4970,11 @@
           <t>All regulatory-relevant logs on certified immutable storage with cryptographic integrity checks.</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4630,6 +5027,11 @@
           <t>Within hours — automated audit-pack generation with a full chain of custody.</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4682,6 +5084,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and real-time access alerts.</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4734,6 +5141,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within the organisation perimeter.</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4786,6 +5198,11 @@
           <t>Automated retention controls, immutable storage, and on-demand CBUAE/SAMA regulatory reporting.</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4838,6 +5255,11 @@
           <t>All regulatory-relevant logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4890,6 +5312,11 @@
           <t>Within hours — automated audit-pack generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4942,6 +5369,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and real-time access alerts for sensitive data.</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4994,6 +5426,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within the country perimeter.</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5046,6 +5483,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulatory evidence packaging.</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5098,6 +5540,11 @@
           <t>All regulatory-relevant logs on certified immutable storage with cryptographic integrity checks.</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5150,6 +5597,11 @@
           <t>Within hours — automated audit-pack generation with a full chain of custody.</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -5202,6 +5654,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and real-time access alerts for sensitive data.</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -5254,6 +5711,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within the licensed jurisdiction.</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -5306,6 +5768,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulatory and settlement audit packs.</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5358,6 +5825,11 @@
           <t>All payment-relevant logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -5410,6 +5882,11 @@
           <t>Within hours — automated dispute and audit-pack generation with chain of custody.</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5462,6 +5939,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and real-time access alerts for payment data.</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5514,6 +5996,11 @@
           <t>Zero data egress enforced technically with continuous compliance monitoring and annual PCI-DSS certification.</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5566,6 +6053,11 @@
           <t>Automated retention controls, immutable storage, and on-demand PCI/scheme audit packs.</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5618,6 +6110,11 @@
           <t>All in-scope payment logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5670,6 +6167,11 @@
           <t>Within hours — automated dispute and audit-pack generation with chain of custody.</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5722,6 +6224,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and real-time alerts for cardholder data access.</t>
         </is>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5774,6 +6281,11 @@
           <t>Zero data egress enforced technically with continuous compliance monitoring and annual certification.</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5826,6 +6338,11 @@
           <t>Automated retention controls, immutable storage, and on-demand audit pack generation for all statutory requirements.</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5878,6 +6395,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity checks and chain of custody.</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5930,6 +6452,11 @@
           <t>Within hours — automated audit pack generation with full chain of custody for statutory submissions.</t>
         </is>
       </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5982,6 +6509,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for sensitive data access.</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6034,6 +6566,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within approved government infrastructure.</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6086,6 +6623,11 @@
           <t>Automated retention controls, immutable storage, and on-demand audit pack generation for all statutory requirements.</t>
         </is>
       </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6138,6 +6680,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity checks and chain of custody.</t>
         </is>
       </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6190,6 +6737,11 @@
           <t>Within hours — automated audit pack generation with full chain of custody for statutory submissions.</t>
         </is>
       </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6242,6 +6794,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for sensitive citizen data access.</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6294,6 +6851,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within approved sovereign infrastructure.</t>
         </is>
       </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6346,6 +6908,11 @@
           <t>Automated retention controls, immutable storage, and on-demand audit evidence generation for all certification scopes.</t>
         </is>
       </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -6398,6 +6965,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -6450,6 +7022,11 @@
           <t>Within hours — automated evidence package generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -6502,6 +7079,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for sensitive data access.</t>
         </is>
       </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -6554,6 +7136,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within contractually required boundaries.</t>
         </is>
       </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6606,6 +7193,11 @@
           <t>Automated retention controls, immutable storage, and on-demand PCI-DSS and DPDP audit evidence.</t>
         </is>
       </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -6658,6 +7250,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6710,6 +7307,11 @@
           <t>Within hours — automated evidence package generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -6762,6 +7364,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for customer data access.</t>
         </is>
       </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -6814,6 +7421,11 @@
           <t>Zero data egress enforced technically with continuous compliance monitoring and PCI-DSS certification.</t>
         </is>
       </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -6866,6 +7478,11 @@
           <t>Automated retention controls, immutable storage, and on-demand PCI-DSS and data protection audit evidence.</t>
         </is>
       </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -6918,6 +7535,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -6970,6 +7592,11 @@
           <t>Within hours — automated evidence package generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -7022,6 +7649,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for customer data access.</t>
         </is>
       </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -7074,6 +7706,11 @@
           <t>Zero data egress enforced technically with continuous compliance monitoring and PCI-DSS certification.</t>
         </is>
       </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -7126,6 +7763,11 @@
           <t>Automated retention controls, immutable storage, and on-demand DoT/TRAI/CERT-In audit packs.</t>
         </is>
       </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -7178,6 +7820,11 @@
           <t>All DoT-mandated records on certified immutable storage with cryptographic integrity and chain of custody.</t>
         </is>
       </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -7230,6 +7877,11 @@
           <t>Within hours — automated audit-pack and lawful interception evidence generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -7282,6 +7934,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and automated alerts for sensitive subscriber data access.</t>
         </is>
       </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -7334,6 +7991,11 @@
           <t>Zero data egress enforced technically — all subscriber data and CDRs ingested, processed, and stored within Indian jurisdiction.</t>
         </is>
       </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -7386,6 +8048,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulator and law enforcement audit packs.</t>
         </is>
       </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -7438,6 +8105,11 @@
           <t>All legally mandated records on certified immutable storage with cryptographic integrity and chain of custody.</t>
         </is>
       </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -7490,6 +8162,11 @@
           <t>Within hours — automated audit-pack and lawful interception evidence generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7542,6 +8219,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and automated alerts for sensitive subscriber data access.</t>
         </is>
       </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -7594,6 +8276,11 @@
           <t>Zero data egress enforced technically — all subscriber data and CDRs stored within applicable jurisdictional boundaries.</t>
         </is>
       </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -7646,6 +8333,11 @@
           <t>Automated retention controls, immutable storage, and on-demand CERC/SERC/CERT-In audit packs.</t>
         </is>
       </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -7698,6 +8390,11 @@
           <t>All CII-relevant logs on certified immutable storage with cryptographic integrity checks and chain of custody.</t>
         </is>
       </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -7750,6 +8447,11 @@
           <t>Within hours — automated audit pack generation with full chain of custody for regulatory submissions.</t>
         </is>
       </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -7802,6 +8504,11 @@
           <t>Zero-trust access across OT and IT with MFA, just-in-time provisioning, and automated alerts for sensitive access.</t>
         </is>
       </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -7854,6 +8561,11 @@
           <t>Zero data egress enforced technically — all operational and consumer data stored within Indian jurisdiction.</t>
         </is>
       </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -7906,6 +8618,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulatory audit packs.</t>
         </is>
       </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -7958,6 +8675,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity checks and chain of custody.</t>
         </is>
       </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -8010,6 +8732,11 @@
           <t>Within hours — automated audit pack generation with full chain of custody for regulatory submissions.</t>
         </is>
       </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8062,6 +8789,11 @@
           <t>Zero-trust access across OT and IT with MFA, just-in-time provisioning, and automated alerts for sensitive access.</t>
         </is>
       </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -8114,6 +8846,11 @@
           <t>Zero data egress enforced technically — all operational and consumer data stored within applicable jurisdictional boundaries.</t>
         </is>
       </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -8166,6 +8903,11 @@
           <t>Automated retention controls, immutable storage, and on-demand evidence generation for all certification and regulatory scopes.</t>
         </is>
       </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -8218,6 +8960,11 @@
           <t>All regulated production records on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -8270,6 +9017,11 @@
           <t>Within hours — automated evidence package generation with full production batch chain of custody.</t>
         </is>
       </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -8322,6 +9074,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and automated alerts for sensitive production data access.</t>
         </is>
       </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -8372,6 +9129,11 @@
       <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Full data lifecycle governance — production records, quality data, and supply chain data retained, protected, and accessible for audit, recall, and ESG reporting.</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
         </is>
       </c>
     </row>
@@ -8386,7 +9148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8399,6 +9161,7 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8452,6 +9215,11 @@
           <t>Option 5 (score 5)</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Option 6 (Not sure / N-A)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8504,6 +9272,11 @@
           <t>APM fully integrated with business observability; every service has SLOs tied to business SLAs.</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8556,6 +9329,11 @@
           <t>Third-party dependencies are part of end-to-end observability with business-impact scoring.</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8608,6 +9386,11 @@
           <t>Full tracing linked to business transaction outcomes and user session context.</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -8660,6 +9443,11 @@
           <t>SLOs are integrated with business impact — error-budget depletion triggers business escalation.</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8712,6 +9500,11 @@
           <t>Full channel observability linked to transaction success rates and customer experience scores.</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -8764,6 +9557,11 @@
           <t>Fully automated infrastructure discovery with real-time topology maps and dependency graphs.</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8816,6 +9614,11 @@
           <t>Full network observability integrated with transaction tracing — network issues linked to business impact.</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8868,6 +9671,11 @@
           <t>ML-driven capacity intelligence linked to business growth forecasts.</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8920,6 +9728,11 @@
           <t>Container, host, and network observability unified with workload context and auto-scaling telemetry.</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8972,6 +9785,11 @@
           <t>Full DC-to-application observability with predictive alerts linked to risk posture.</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9024,6 +9842,11 @@
           <t>Full log data lake — all systems, all tiers, with real-time streaming and fast query.</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9076,6 +9899,11 @@
           <t>Tiered storage (hot/warm/cold) with regulatory-aligned retention and real-time query across all tiers.</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9128,6 +9956,11 @@
           <t>ML anomaly detection, automated pattern clustering, and natural-language log query.</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9180,6 +10013,11 @@
           <t>Fully managed log lifecycle with ML-driven tiering, deduplication, and per-source cost attribution.</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -9230,6 +10068,11 @@
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>ML-powered log intelligence — behavioural baselines, multi-source correlation, SOAR integration.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
         </is>
       </c>
     </row>
@@ -9244,7 +10087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:K166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9257,6 +10100,7 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9310,6 +10154,11 @@
           <t>Option 5 (score 5)</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Option 6 (Not sure / N-A)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -9362,6 +10211,11 @@
           <t>Full business transaction observability — IT metrics linked to business SLAs, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9414,6 +10268,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to business KPIs.</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -9466,6 +10325,11 @@
           <t>A unified Business Observability platform — IT and business share a single source of truth.</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9518,6 +10382,11 @@
           <t>Fully automated synthetic testing in production and pre-prod with business-impact scoring per journey.</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9570,6 +10439,11 @@
           <t>Full alignment — observability drives business SLA reporting, regulatory submissions, and P&amp;L impact assessments.</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9622,6 +10496,11 @@
           <t>Full business transaction observability — IT metrics linked to business SLAs, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9674,6 +10553,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to business KPIs.</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9726,6 +10610,11 @@
           <t>A unified Business Observability platform — IT and business share a single source of truth.</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9778,6 +10667,11 @@
           <t>Fully automated synthetic testing across all channels with business-impact scoring per journey.</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9830,6 +10724,11 @@
           <t>Full alignment — observability drives regulatory submissions, SLA reporting, and business impact assessments.</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9882,6 +10781,11 @@
           <t>Full business transaction observability — IT metrics linked to business SLAs, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9934,6 +10838,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to business KPIs.</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9986,6 +10895,11 @@
           <t>A unified Business Observability platform — IT and business share a single source of truth.</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -10038,6 +10952,11 @@
           <t>Fully automated synthetic testing across all channels with business-impact scoring per journey.</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -10090,6 +11009,11 @@
           <t>Full alignment — observability directly feeds regulatory reporting, incident notifications, and board-level resilience scorecards.</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -10142,6 +11066,11 @@
           <t>Full payment orchestration observability — each instrument mapped to SLA targets, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -10194,6 +11123,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to settlement SLAs.</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -10246,6 +11180,11 @@
           <t>A unified payments observability platform — IT, finance, and compliance share one view.</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -10298,6 +11237,11 @@
           <t>All third-party dependencies are part of end-to-end transaction observability with business-impact scoring.</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -10350,6 +11294,11 @@
           <t>Full alignment — observability directly feeds regulatory reporting, merchant SLAs, and chargeback analysis.</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -10402,6 +11351,11 @@
           <t>Full payment orchestration observability — every instrument mapped to SLA targets, failures trigger automated triage.</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -10454,6 +11408,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to settlement SLAs.</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -10506,6 +11465,11 @@
           <t>A unified payments observability platform — IT, finance, and compliance share one live view.</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -10558,6 +11522,11 @@
           <t>All third-party dependencies are part of end-to-end transaction observability with business-impact scoring.</t>
         </is>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -10610,6 +11579,11 @@
           <t>Full alignment — observability directly feeds scheme reporting, merchant SLA dashboards, and chargeback analysis.</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -10662,6 +11636,11 @@
           <t>Full citizen service observability — IT metrics linked to programme SLAs and citizen experience outcomes.</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -10714,6 +11693,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection with automated escalation to the programme team.</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -10766,6 +11750,11 @@
           <t>A unified digital service observability platform — IT and programme management share one view.</t>
         </is>
       </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10818,6 +11807,11 @@
           <t>Fully automated synthetic testing with business-impact scoring per citizen service.</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -10870,6 +11864,11 @@
           <t>Full alignment — observability feeds programme KPI dashboards, ministerial reporting, and audit submissions.</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -10922,6 +11921,11 @@
           <t>Full citizen service observability — IT metrics linked to programme SLAs and citizen experience outcomes.</t>
         </is>
       </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -10974,6 +11978,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection with automated escalation to the programme team.</t>
         </is>
       </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -11026,6 +12035,11 @@
           <t>A unified digital service observability platform — IT and programme management share one live view.</t>
         </is>
       </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -11078,6 +12092,11 @@
           <t>Fully automated synthetic testing with business-impact scoring per citizen service.</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -11130,6 +12149,11 @@
           <t>Full alignment — observability feeds programme dashboards, ministerial reporting, and audit submissions.</t>
         </is>
       </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -11182,6 +12206,11 @@
           <t>Full product observability — every customer journey mapped to SLA targets with automated triage on failure.</t>
         </is>
       </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -11234,6 +12263,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection with deployment context and customer impact scoring.</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -11286,6 +12320,11 @@
           <t>A unified product observability platform shared by engineering, CS, and account management.</t>
         </is>
       </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -11338,6 +12377,11 @@
           <t>Continuous synthetic testing in production and staging with business-impact scoring per journey.</t>
         </is>
       </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -11390,6 +12434,11 @@
           <t>Full alignment — observability feeds customer SLA reporting, renewal risk dashboards, and executive scorecards.</t>
         </is>
       </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -11442,6 +12491,11 @@
           <t>Full omnichannel transaction observability — every customer journey mapped to conversion and revenue KPIs with automated triage.</t>
         </is>
       </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -11494,6 +12548,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to GMV and conversion metrics.</t>
         </is>
       </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -11546,6 +12605,11 @@
           <t>A unified commerce observability platform — IT, merchandising, and commercial share one live view.</t>
         </is>
       </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -11598,6 +12662,11 @@
           <t>Continuous synthetic testing with GMV-impact scoring per journey degradation.</t>
         </is>
       </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -11650,6 +12719,11 @@
           <t>Full alignment — observability directly drives incident prioritisation, sale-event capacity planning, and P&amp;L impact reporting.</t>
         </is>
       </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -11702,6 +12776,11 @@
           <t>Full omnichannel transaction observability — every customer journey mapped to conversion and revenue KPIs with automated triage.</t>
         </is>
       </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -11754,6 +12833,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to GMV and conversion metrics.</t>
         </is>
       </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -11806,6 +12890,11 @@
           <t>A unified commerce observability platform — IT, merchandising, and commercial share one live view.</t>
         </is>
       </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -11858,6 +12947,11 @@
           <t>Continuous synthetic testing with GMV-impact scoring per journey degradation.</t>
         </is>
       </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -11910,6 +13004,11 @@
           <t>Full alignment — observability directly drives incident prioritisation, peak-event capacity planning, and revenue impact reporting.</t>
         </is>
       </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -11962,6 +13061,11 @@
           <t>Full end-to-end service observability — network, IT, and BSS metrics linked to subscriber experience KPIs with automated triage.</t>
         </is>
       </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -12014,6 +13118,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to subscriber experience and ARPU impact.</t>
         </is>
       </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -12066,6 +13175,11 @@
           <t>A unified telecom service observability platform shared across NOC, commercial, CX, and regulatory functions.</t>
         </is>
       </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -12118,6 +13232,11 @@
           <t>Continuous synthetic service testing with subscriber experience scoring and automated incident creation.</t>
         </is>
       </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -12170,6 +13289,11 @@
           <t>Full alignment — observability feeds TRAI regulatory submissions, interconnect SLA reporting, and subscriber experience dashboards.</t>
         </is>
       </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -12222,6 +13346,11 @@
           <t>Full end-to-end service observability — network, IT, and BSS metrics linked to subscriber experience KPIs with automated triage.</t>
         </is>
       </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -12274,6 +13403,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to subscriber experience and ARPU impact.</t>
         </is>
       </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -12326,6 +13460,11 @@
           <t>A unified telecom service observability platform shared across NOC, commercial, CX, and regulatory functions.</t>
         </is>
       </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -12378,6 +13517,11 @@
           <t>Continuous synthetic service testing with subscriber experience scoring and automated incident creation.</t>
         </is>
       </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -12430,6 +13574,11 @@
           <t>Full alignment — observability feeds regulatory submissions, interconnect SLA reporting, and subscriber experience dashboards.</t>
         </is>
       </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -12482,6 +13631,11 @@
           <t>Full operational transaction observability — SCADA, OMS, billing, and metering linked to regulatory SLAs with automated triage.</t>
         </is>
       </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -12534,6 +13688,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to grid SLAs and regulatory reliability indices.</t>
         </is>
       </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12586,6 +13745,11 @@
           <t>A unified utility operations platform — grid, commercial, and regulatory teams share one live view.</t>
         </is>
       </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12638,6 +13802,11 @@
           <t>Continuous end-to-end operational monitoring with regulatory reliability impact scoring.</t>
         </is>
       </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12690,6 +13859,11 @@
           <t>Full alignment — observability directly feeds regulatory submissions, SAIDI/SAIFI reporting, and tariff proceedings.</t>
         </is>
       </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12742,6 +13916,11 @@
           <t>Full operational transaction observability — SCADA, OMS, billing, and metering linked to regulatory SLAs with automated triage.</t>
         </is>
       </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12794,6 +13973,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to grid SLAs and regulatory reliability indices.</t>
         </is>
       </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12846,6 +14030,11 @@
           <t>A unified utility operations platform — grid, commercial, and regulatory teams share one live view.</t>
         </is>
       </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12898,6 +14087,11 @@
           <t>Continuous end-to-end operational monitoring with regulatory reliability impact scoring.</t>
         </is>
       </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12950,6 +14144,11 @@
           <t>Full alignment — observability directly feeds regulatory submissions, reliability index reporting, and tariff proceedings.</t>
         </is>
       </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13002,6 +14201,11 @@
           <t>Full manufacturing transaction observability — ERP, MES, SCADA, and QMS metrics linked to delivery and quality SLAs with automated triage.</t>
         </is>
       </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13054,6 +14258,11 @@
           <t>Under 5 minutes — ML-driven anomaly detection linked to OEE and delivery SLA impact.</t>
         </is>
       </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13106,6 +14315,11 @@
           <t>A unified manufacturing intelligence platform — operations, supply chain, quality, and commercial share one live view.</t>
         </is>
       </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13158,6 +14372,11 @@
           <t>Continuous end-to-end operational health monitoring with OEE and delivery commitment impact scoring.</t>
         </is>
       </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13210,6 +14429,11 @@
           <t>Full alignment — observability directly drives incident prioritisation, capacity planning, and customer delivery SLA reporting.</t>
         </is>
       </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13262,6 +14486,11 @@
           <t>APM fully integrated with business observability; every service has SLOs tied to business SLAs.</t>
         </is>
       </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13314,6 +14543,11 @@
           <t>Third-party dependencies are part of end-to-end observability with business-impact scoring.</t>
         </is>
       </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -13366,6 +14600,11 @@
           <t>Full tracing linked to business transaction outcomes and user session context.</t>
         </is>
       </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -13418,6 +14657,11 @@
           <t>SLOs are integrated with business impact — error-budget depletion triggers business escalation.</t>
         </is>
       </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -13470,6 +14714,11 @@
           <t>Full channel observability linked to transaction success rates and customer experience scores.</t>
         </is>
       </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -13522,6 +14771,11 @@
           <t>Fully automated infrastructure discovery with real-time topology maps and dependency graphs.</t>
         </is>
       </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -13574,6 +14828,11 @@
           <t>Full network observability integrated with transaction tracing — network issues linked to business impact.</t>
         </is>
       </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -13626,6 +14885,11 @@
           <t>ML-driven capacity intelligence linked to business growth forecasts.</t>
         </is>
       </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -13678,6 +14942,11 @@
           <t>Container, host, and network observability unified with workload context and auto-scaling telemetry.</t>
         </is>
       </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -13730,6 +14999,11 @@
           <t>Full DC-to-application observability with predictive alerts linked to risk posture.</t>
         </is>
       </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -13782,6 +15056,11 @@
           <t>Full log data lake — all systems, all tiers, with real-time streaming and fast query.</t>
         </is>
       </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -13834,6 +15113,11 @@
           <t>Tiered storage (hot/warm/cold) with regulatory-aligned retention and real-time query across all tiers.</t>
         </is>
       </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -13886,6 +15170,11 @@
           <t>ML anomaly detection, automated pattern clustering, and natural-language log query.</t>
         </is>
       </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -13938,6 +15227,11 @@
           <t>Fully managed log lifecycle with ML-driven tiering, deduplication, and per-source cost attribution.</t>
         </is>
       </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -13990,6 +15284,11 @@
           <t>ML-powered log intelligence — behavioural baselines, multi-source correlation, SOAR integration.</t>
         </is>
       </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -14042,6 +15341,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulatory reporting.</t>
         </is>
       </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -14094,6 +15398,11 @@
           <t>All regulatory-relevant logs on certified immutable storage with cryptographic integrity checks.</t>
         </is>
       </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -14146,6 +15455,11 @@
           <t>Within hours — automated audit-pack generation with a full chain of custody.</t>
         </is>
       </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -14198,6 +15512,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and real-time access alerts.</t>
         </is>
       </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -14250,6 +15569,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within the organisation perimeter.</t>
         </is>
       </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -14302,6 +15626,11 @@
           <t>Automated retention controls, immutable storage, and on-demand CBUAE/SAMA regulatory reporting.</t>
         </is>
       </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -14354,6 +15683,11 @@
           <t>All regulatory-relevant logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -14406,6 +15740,11 @@
           <t>Within hours — automated audit-pack generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -14458,6 +15797,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and real-time access alerts for sensitive data.</t>
         </is>
       </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -14510,6 +15854,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within the country perimeter.</t>
         </is>
       </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -14562,6 +15911,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulatory evidence packaging.</t>
         </is>
       </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -14614,6 +15968,11 @@
           <t>All regulatory-relevant logs on certified immutable storage with cryptographic integrity checks.</t>
         </is>
       </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -14666,6 +16025,11 @@
           <t>Within hours — automated audit-pack generation with a full chain of custody.</t>
         </is>
       </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -14718,6 +16082,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and real-time access alerts for sensitive data.</t>
         </is>
       </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -14770,6 +16139,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within the licensed jurisdiction.</t>
         </is>
       </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -14822,6 +16196,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulatory and settlement audit packs.</t>
         </is>
       </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -14874,6 +16253,11 @@
           <t>All payment-relevant logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -14926,6 +16310,11 @@
           <t>Within hours — automated dispute and audit-pack generation with chain of custody.</t>
         </is>
       </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -14978,6 +16367,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and real-time access alerts for payment data.</t>
         </is>
       </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -15030,6 +16424,11 @@
           <t>Zero data egress enforced technically with continuous compliance monitoring and annual PCI-DSS certification.</t>
         </is>
       </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -15082,6 +16481,11 @@
           <t>Automated retention controls, immutable storage, and on-demand PCI/scheme audit packs.</t>
         </is>
       </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -15134,6 +16538,11 @@
           <t>All in-scope payment logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -15186,6 +16595,11 @@
           <t>Within hours — automated dispute and audit-pack generation with chain of custody.</t>
         </is>
       </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -15238,6 +16652,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and real-time alerts for cardholder data access.</t>
         </is>
       </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -15290,6 +16709,11 @@
           <t>Zero data egress enforced technically with continuous compliance monitoring and annual certification.</t>
         </is>
       </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -15342,6 +16766,11 @@
           <t>Automated retention controls, immutable storage, and on-demand audit pack generation for all statutory requirements.</t>
         </is>
       </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -15394,6 +16823,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity checks and chain of custody.</t>
         </is>
       </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -15446,6 +16880,11 @@
           <t>Within hours — automated audit pack generation with full chain of custody for statutory submissions.</t>
         </is>
       </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -15498,6 +16937,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for sensitive data access.</t>
         </is>
       </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -15550,6 +16994,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within approved government infrastructure.</t>
         </is>
       </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -15602,6 +17051,11 @@
           <t>Automated retention controls, immutable storage, and on-demand audit pack generation for all statutory requirements.</t>
         </is>
       </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -15654,6 +17108,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity checks and chain of custody.</t>
         </is>
       </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -15706,6 +17165,11 @@
           <t>Within hours — automated audit pack generation with full chain of custody for statutory submissions.</t>
         </is>
       </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -15758,6 +17222,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for sensitive citizen data access.</t>
         </is>
       </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -15810,6 +17279,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within approved sovereign infrastructure.</t>
         </is>
       </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -15862,6 +17336,11 @@
           <t>Automated retention controls, immutable storage, and on-demand audit evidence generation for all certification scopes.</t>
         </is>
       </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -15914,6 +17393,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -15966,6 +17450,11 @@
           <t>Within hours — automated evidence package generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -16018,6 +17507,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for sensitive data access.</t>
         </is>
       </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -16070,6 +17564,11 @@
           <t>Zero data egress enforced technically — all logs ingested, processed, and stored within contractually required boundaries.</t>
         </is>
       </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -16122,6 +17621,11 @@
           <t>Automated retention controls, immutable storage, and on-demand PCI-DSS and DPDP audit evidence.</t>
         </is>
       </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -16174,6 +17678,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -16226,6 +17735,11 @@
           <t>Within hours — automated evidence package generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -16278,6 +17792,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for customer data access.</t>
         </is>
       </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -16330,6 +17849,11 @@
           <t>Zero data egress enforced technically with continuous compliance monitoring and PCI-DSS certification.</t>
         </is>
       </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -16382,6 +17906,11 @@
           <t>Automated retention controls, immutable storage, and on-demand PCI-DSS and data protection audit evidence.</t>
         </is>
       </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -16434,6 +17963,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -16486,6 +18020,11 @@
           <t>Within hours — automated evidence package generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -16538,6 +18077,11 @@
           <t>Zero-trust log access with MFA, just-in-time provisioning, and automated alerts for customer data access.</t>
         </is>
       </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -16590,6 +18134,11 @@
           <t>Zero data egress enforced technically with continuous compliance monitoring and PCI-DSS certification.</t>
         </is>
       </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -16642,6 +18191,11 @@
           <t>Automated retention controls, immutable storage, and on-demand DoT/TRAI/CERT-In audit packs.</t>
         </is>
       </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -16694,6 +18248,11 @@
           <t>All DoT-mandated records on certified immutable storage with cryptographic integrity and chain of custody.</t>
         </is>
       </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -16746,6 +18305,11 @@
           <t>Within hours — automated audit-pack and lawful interception evidence generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -16798,6 +18362,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and automated alerts for sensitive subscriber data access.</t>
         </is>
       </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -16850,6 +18419,11 @@
           <t>Zero data egress enforced technically — all subscriber data and CDRs ingested, processed, and stored within Indian jurisdiction.</t>
         </is>
       </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -16902,6 +18476,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulator and law enforcement audit packs.</t>
         </is>
       </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -16954,6 +18533,11 @@
           <t>All legally mandated records on certified immutable storage with cryptographic integrity and chain of custody.</t>
         </is>
       </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -17006,6 +18590,11 @@
           <t>Within hours — automated audit-pack and lawful interception evidence generation with full chain of custody.</t>
         </is>
       </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -17058,6 +18647,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and automated alerts for sensitive subscriber data access.</t>
         </is>
       </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -17110,6 +18704,11 @@
           <t>Zero data egress enforced technically — all subscriber data and CDRs stored within applicable jurisdictional boundaries.</t>
         </is>
       </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -17162,6 +18761,11 @@
           <t>Automated retention controls, immutable storage, and on-demand CERC/SERC/CERT-In audit packs.</t>
         </is>
       </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -17214,6 +18818,11 @@
           <t>All CII-relevant logs on certified immutable storage with cryptographic integrity checks and chain of custody.</t>
         </is>
       </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -17266,6 +18875,11 @@
           <t>Within hours — automated audit pack generation with full chain of custody for regulatory submissions.</t>
         </is>
       </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -17318,6 +18932,11 @@
           <t>Zero-trust access across OT and IT with MFA, just-in-time provisioning, and automated alerts for sensitive access.</t>
         </is>
       </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -17370,6 +18989,11 @@
           <t>Zero data egress enforced technically — all operational and consumer data stored within Indian jurisdiction.</t>
         </is>
       </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -17422,6 +19046,11 @@
           <t>Automated retention controls, immutable storage, and on-demand regulatory audit packs.</t>
         </is>
       </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -17474,6 +19103,11 @@
           <t>All in-scope logs on certified immutable storage with cryptographic integrity checks and chain of custody.</t>
         </is>
       </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -17526,6 +19160,11 @@
           <t>Within hours — automated audit pack generation with full chain of custody for regulatory submissions.</t>
         </is>
       </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -17578,6 +19217,11 @@
           <t>Zero-trust access across OT and IT with MFA, just-in-time provisioning, and automated alerts for sensitive access.</t>
         </is>
       </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -17630,6 +19274,11 @@
           <t>Zero data egress enforced technically — all operational and consumer data stored within applicable jurisdictional boundaries.</t>
         </is>
       </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -17682,6 +19331,11 @@
           <t>Automated retention controls, immutable storage, and on-demand evidence generation for all certification and regulatory scopes.</t>
         </is>
       </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -17734,6 +19388,11 @@
           <t>All regulated production records on certified immutable storage with cryptographic integrity verification.</t>
         </is>
       </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -17786,6 +19445,11 @@
           <t>Within hours — automated evidence package generation with full production batch chain of custody.</t>
         </is>
       </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -17838,6 +19502,11 @@
           <t>Zero-trust access with MFA, just-in-time provisioning, and automated alerts for sensitive production data access.</t>
         </is>
       </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -17888,6 +19557,11 @@
       <c r="J166" s="2" t="inlineStr">
         <is>
           <t>Full data lifecycle governance — production records, quality data, and supply chain data retained, protected, and accessible for audit, recall, and ESG reporting.</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Not sure / not applicable to my role — I don’t have visibility into this</t>
         </is>
       </c>
     </row>
